--- a/samples/ss_muarakarang_durikosambi_ingest.xlsx
+++ b/samples/ss_muarakarang_durikosambi_ingest.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,20 @@
       <c r="D3" s="3" t="n">
         <v>76</v>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>GABUNGAN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Gabungan Muarakarang - Durikosambi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
